--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_capacity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_utilization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74EC4D7-04EC-4ADE-A426-E298D036B6C6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6904D-1765-4F4F-8EC1-21127141713F}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Capacity" sheetId="1" r:id="rId1"/>
+    <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" fullPrecision="0"/>
 </workbook>
@@ -40,7 +40,7 @@
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>Device Capacity</t>
+    <t>Device Utilization Rate</t>
   </si>
 </sst>
 </file>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\stefan\aspect\api\templates\device_utilization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6904D-1765-4F4F-8EC1-21127141713F}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB80D8D-D791-4D9C-9C8D-E52862162874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1509" yWindow="746" windowWidth="25945" windowHeight="17768" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -84,6 +84,13 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,7 +130,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -167,15 +174,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -219,6 +228,7 @@
     <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="43" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -556,45 +566,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\stefan\aspect\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\device_utilization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB80D8D-D791-4D9C-9C8D-E52862162874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1509" yWindow="746" windowWidth="25945" windowHeight="17768" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1512" yWindow="744" windowWidth="25944" windowHeight="17772" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" fullPrecision="0"/>
+  <calcPr calcId="162913" fullPrecision="0"/>
 </workbook>
 </file>
 
@@ -28,13 +27,7 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
     <t>Device</t>
-  </si>
-  <si>
-    <t>LGA: &lt;Lgas&gt;</t>
   </si>
   <si>
     <t>&lt;name&gt;</t>
@@ -42,11 +35,17 @@
   <si>
     <t>Device Utilization Rate</t>
   </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -230,8 +229,36 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="43" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -564,49 +591,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:1" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\device_utilization\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Utilization Rate" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,40 +26,35 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t xml:space="preserve">Device Utilization Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;Table&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;name&gt;</t>
+    <t>Device Utilization Rate</t>
+  </si>
+  <si>
+    <t>Dates: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="0.00%"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -64,22 +63,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -87,8 +71,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -109,84 +100,78 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -245,72 +230,341 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11.015625" defaultRowHeight="15.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.9"/>
+    <col min="1" max="1" width="31.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10309"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D354144C-9BB6-FA41-B306-2D81F780EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -53,7 +65,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -99,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -122,21 +134,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -167,7 +191,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -513,53 +537,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\device_utilization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FB9D02-8537-7A47-BEEE-5302290BCA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Device Utilization Rate</t>
   </si>
@@ -48,12 +49,15 @@
   </si>
   <si>
     <t>&lt;name&gt;</t>
+  </si>
+  <si>
+    <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -127,16 +131,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -167,7 +172,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -513,57 +518,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:I4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FB9D02-8537-7A47-BEEE-5302290BCA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72224212-388E-EE4B-8262-8FC9D61CB82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Device Utilization Rate</t>
   </si>
@@ -52,6 +63,12 @@
   </si>
   <si>
     <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
+  </si>
+  <si>
+    <t>Daily Capacity</t>
+  </si>
+  <si>
+    <t>&lt;dailyTestCapacity&gt;</t>
   </si>
 </sst>
 </file>
@@ -131,7 +148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -142,6 +159,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,6 +544,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
@@ -573,19 +595,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72224212-388E-EE4B-8262-8FC9D61CB82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Utilization Rate" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Utilization Rate" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Device Utilization Rate</t>
   </si>
@@ -44,6 +22,9 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
+  </si>
+  <si>
     <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
   </si>
   <si>
@@ -59,13 +40,16 @@
     <t>Device</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Daily Capacity</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
-  </si>
-  <si>
-    <t>Daily Capacity</t>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;dailyTestCapacity&gt;</t>
@@ -74,36 +58,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,143 +113,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD7D7D7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -539,88 +417,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,98 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Utilization Rate" state="visible" r:id="rId4"/>
+    <sheet name="Utilization Rate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Device Utilization Rate</t>
-  </si>
-  <si>
-    <t>Dates: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Table&gt;</t>
-  </si>
-  <si>
-    <t>Device</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Daily Capacity</t>
-  </si>
-  <si>
-    <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
-    <t>&lt;dailyTestCapacity&gt;</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
       <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
-      <family val="2"/>
       <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <charset val="1"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
-      <family val="2"/>
       <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
       <charset val="1"/>
       <family val="2"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -104,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,45 +70,120 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,104 +449,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col width="36" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="31.83" customWidth="1" min="2" max="2"/>
+    <col width="10.16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Device Utilization Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dates: &lt;Dates&gt;</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>&lt;Table&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Daily Capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="5">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>&lt;siteName&gt;</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>&lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>&lt;dailyTestCapacity&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1"/>
+    <row r="11" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -1,58 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Utilization Rate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Utilization Rate" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Device Utilization Rate</t>
+  </si>
+  <si>
+    <t>Dates: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>Daily Capacity</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dailyTestCapacity&gt;</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="16"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <charset val="1"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="16"/>
-    </font>
-    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -70,18 +119,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
@@ -89,101 +130,42 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -449,107 +431,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11" customHeight="1"/>
   <cols>
-    <col width="36" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="31.83" customWidth="1" min="2" max="2"/>
-    <col width="10.16" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="31.83" customWidth="1"/>
+    <col min="3" max="3" width="10.16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Device Utilization Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dates: &lt;Dates&gt;</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Device percentages are not weighted by their capacity. Therefore, the simple average of these values may differ from the total percentage shown in the system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>&lt;Table&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Daily Capacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="5">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>&lt;siteName&gt;</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>&lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>&lt;dailyTestCapacity&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1"/>
-    <row r="11" ht="15" customHeight="1"/>
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -142,9 +142,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>

--- a/api/templates/device_utilization/en.xlsx
+++ b/api/templates/device_utilization/en.xlsx
@@ -34,7 +34,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -142,7 +142,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
